--- a/education_forms/034_student_of_the_year_form--education_forms.xlsx
+++ b/education_forms/034_student_of_the_year_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -901,16 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-_arts
--_engineering
--_science</t>
+          <t>-_arts_-_engineering_-_science</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>- Arts
-- Engineering
-- Science</t>
+          <t>- Arts - Engineering - Science</t>
         </is>
       </c>
     </row>
@@ -939,16 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-_1st
--_2nd
--_3rd</t>
+          <t>-_1st_-_2nd_-_3rd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>- 1st
-- 2nd
-- 3rd</t>
+          <t>- 1st - 2nd - 3rd</t>
         </is>
       </c>
     </row>
@@ -977,16 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-_2022
--_2023
--_2024</t>
+          <t>-_2022_-_2023_-_2024</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>- 2022
-- 2023
-- 2024</t>
+          <t>- 2022 - 2023 - 2024</t>
         </is>
       </c>
     </row>
@@ -1015,16 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-_2022
--_2023
--_2024</t>
+          <t>-_2022_-_2023_-_2024</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>- 2022
-- 2023
-- 2024</t>
+          <t>- 2022 - 2023 - 2024</t>
         </is>
       </c>
     </row>
